--- a/artfynd/A 21081-2025 artfynd.xlsx
+++ b/artfynd/A 21081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874420</v>
+        <v>124874390</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574982</v>
+        <v>574991</v>
       </c>
       <c r="R2" t="n">
-        <v>6415077</v>
+        <v>6415068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874390</v>
+        <v>124874420</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574991</v>
+        <v>574982</v>
       </c>
       <c r="R3" t="n">
-        <v>6415068</v>
+        <v>6415077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21081-2025 artfynd.xlsx
+++ b/artfynd/A 21081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874390</v>
+        <v>124874420</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574991</v>
+        <v>574982</v>
       </c>
       <c r="R2" t="n">
-        <v>6415068</v>
+        <v>6415077</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874420</v>
+        <v>124874390</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574982</v>
+        <v>574991</v>
       </c>
       <c r="R3" t="n">
-        <v>6415077</v>
+        <v>6415068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21081-2025 artfynd.xlsx
+++ b/artfynd/A 21081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124874420</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>124874390</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21081-2025 artfynd.xlsx
+++ b/artfynd/A 21081-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>91166</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>NT</t>
@@ -793,11 +788,6 @@
       </c>
       <c r="B3" t="n">
         <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21081-2025 artfynd.xlsx
+++ b/artfynd/A 21081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124874420</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>124874390</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
